--- a/product_selector_out/STM32C5 series.xlsx
+++ b/product_selector_out/STM32C5 series.xlsx
@@ -20607,7 +20607,7 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23550,7 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -47122,9 +47122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -47187,14 +47187,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S71" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -47422,9 +47422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -47449,9 +47449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -47514,14 +47514,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -47749,9 +47749,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49411,9 +49411,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -49476,14 +49476,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R78" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S78" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -49711,9 +49711,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50065,9 +50065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -50130,14 +50130,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R80" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S80" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T80" s="6" t="inlineStr">
@@ -50365,9 +50365,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50392,9 +50392,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -50457,14 +50457,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R81" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S81" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -50692,9 +50692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53983,7 +53983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -56613,7 +56613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32C5A3VG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -56628,14 +56628,14 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32C5A3VG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -56650,14 +56650,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32C5A3ZG</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -56672,14 +56672,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32C5A3ZG</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -56694,14 +56694,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -56723,7 +56723,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -56745,7 +56745,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -56767,7 +56767,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -56789,7 +56789,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -56811,7 +56811,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56833,7 +56833,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56855,7 +56855,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -56877,7 +56877,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -56899,7 +56899,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -56921,7 +56921,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32C5A3RG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -56936,14 +56936,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32C5A3RG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -56958,14 +56958,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -56987,7 +56987,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -57009,7 +57009,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32C5A3KG</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -57024,14 +57024,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32C5A3KG</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -57046,14 +57046,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32C5A3MG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -57068,14 +57068,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32C5A3MG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -57090,14 +57090,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C5A3CG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -57112,14 +57112,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C5A3CG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -57134,14 +57134,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C593VG</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -57163,7 +57163,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C593VG</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -57185,7 +57185,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C593ZE</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -57207,7 +57207,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C593ZE</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -57229,7 +57229,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C591CE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -57251,7 +57251,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C591CE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -57273,7 +57273,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C591CG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -57295,7 +57295,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C591CG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -57309,226 +57309,6 @@
         </is>
       </c>
       <c r="D151" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>STM32C5A3CG</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>STM32C5A3CG</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>STM32C593VG</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>STM32C593VG</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>STM32C593ZE</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>STM32C593ZE</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>STM32C591CE</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>STM32C591CE</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>STM32C591CG</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>STM32C591CG</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32C5 series.xlsx
+++ b/product_selector_out/STM32C5 series.xlsx
@@ -20607,7 +20607,7 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -23550,7 +23550,7 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
     </row>
@@ -47122,9 +47122,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -47187,14 +47187,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
@@ -47422,9 +47422,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM71" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -47449,9 +47449,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -47514,14 +47514,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T72" s="6" t="inlineStr">
@@ -47749,9 +47749,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49411,9 +49411,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -49476,14 +49476,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S78" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T78" s="6" t="inlineStr">
@@ -49711,9 +49711,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM78" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50065,9 +50065,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -50130,14 +50130,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T80" s="6" t="inlineStr">
@@ -50365,9 +50365,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM80" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -50392,9 +50392,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -50457,14 +50457,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S81" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="S81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
@@ -50692,9 +50692,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM81" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -53983,7 +53983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -56613,7 +56613,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C5A3VG</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -56628,14 +56628,14 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32C591RG</t>
+          <t>STM32C5A3VG</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -56650,14 +56650,14 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C5A3ZG</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -56672,14 +56672,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32C593CE</t>
+          <t>STM32C5A3ZG</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -56694,14 +56694,14 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -56723,7 +56723,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32C593CG</t>
+          <t>STM32C591RG</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -56745,7 +56745,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -56767,7 +56767,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32C591ZE</t>
+          <t>STM32C593CE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -56789,7 +56789,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -56811,7 +56811,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32C591ZG</t>
+          <t>STM32C593CG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -56833,7 +56833,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -56855,7 +56855,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32C591RE</t>
+          <t>STM32C591ZE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -56877,7 +56877,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -56899,7 +56899,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STM32C593RG</t>
+          <t>STM32C591ZG</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -56921,7 +56921,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C5A3RG</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -56936,14 +56936,14 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STM32C593VE</t>
+          <t>STM32C5A3RG</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -56958,14 +56958,14 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -56987,7 +56987,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>STM32C593MG</t>
+          <t>STM32C591RE</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -57009,7 +57009,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C5A3KG</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -57024,14 +57024,14 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STM32C593RE</t>
+          <t>STM32C5A3KG</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -57046,14 +57046,14 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C5A3MG</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -57068,14 +57068,14 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32C593ZG</t>
+          <t>STM32C5A3MG</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -57090,14 +57090,14 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32C5A3CG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -57112,14 +57112,14 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32C5A3CG</t>
+          <t>STM32C593RG</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -57134,14 +57134,14 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32C593VG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -57163,7 +57163,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32C593VG</t>
+          <t>STM32C593VE</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -57185,7 +57185,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32C593ZE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -57207,7 +57207,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32C593ZE</t>
+          <t>STM32C593MG</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -57229,7 +57229,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32C591CE</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -57251,7 +57251,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STM32C591CE</t>
+          <t>STM32C593RE</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -57273,7 +57273,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>STM32C591CG</t>
+          <t>STM32C593ZG</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -57295,20 +57295,240 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>STM32C593ZG</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32C5A3CG</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>STM32C5A3CG</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32C593VG</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32C593VG</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32C593ZE</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32C593ZE</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32C591CE</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32C591CE</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Timers (32-bit) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>STM32C591CG</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32C591CG</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
         <is>
           <t>Timers (32-bit) typ</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>Table 5. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>

--- a/product_selector_out/STM32C5 series.xlsx
+++ b/product_selector_out/STM32C5 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM91"/>
+  <dimension ref="A1:BN91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.0625" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c562ce.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c551cc.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c542cc.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c542cc.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c542cc.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c542cc.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c542cc.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -15702,6 +15929,11 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c532cb.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -20280,6 +20577,11 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -20934,6 +21241,11 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -24204,6 +24561,11 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -24858,6 +25225,11 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -25512,6 +25889,11 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c5a3cg.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -26820,6 +27217,11 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
@@ -27147,12 +27549,17 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32c591ce.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -27173,16 +27580,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -27195,6 +27600,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -27214,7 +27620,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -27311,7 +27719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM91"/>
+  <dimension ref="A1:BN91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -27379,6 +27787,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27712,6 +28121,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -27807,6 +28221,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -28129,7 +28544,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28456,7 +28876,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28783,7 +29208,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29110,7 +29540,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29437,7 +29872,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29764,7 +30204,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30091,7 +30536,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30418,7 +30868,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30745,7 +31200,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31072,7 +31532,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31399,7 +31864,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31726,7 +32196,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32053,7 +32528,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32380,7 +32860,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32707,7 +33192,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33034,7 +33524,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33361,7 +33856,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33688,7 +34188,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34015,7 +34520,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34342,7 +34852,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34669,7 +35184,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34996,7 +35516,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35323,7 +35848,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35650,7 +36180,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35977,7 +36512,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36304,7 +36844,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36631,7 +37176,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36958,7 +37508,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37285,7 +37840,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37612,7 +38172,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37939,7 +38504,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38266,7 +38836,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38593,7 +39168,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38920,7 +39500,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39247,7 +39832,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39574,7 +40164,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39901,7 +40496,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40228,7 +40828,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40555,7 +41160,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40882,7 +41492,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41209,7 +41824,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41536,7 +42156,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41863,7 +42488,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42190,7 +42820,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42517,7 +43152,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42844,7 +43484,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43171,7 +43816,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43498,7 +44148,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43825,7 +44480,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44152,7 +44812,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44479,7 +45144,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44806,7 +45476,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45133,7 +45808,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45460,7 +46140,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45787,7 +46472,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46114,7 +46804,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46441,7 +47136,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46768,7 +47468,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47095,7 +47800,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN70" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47422,7 +48132,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47749,7 +48464,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN72" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48076,7 +48796,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48403,7 +49128,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48730,7 +49460,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49057,7 +49792,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49384,7 +50124,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49711,7 +50456,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50038,7 +50788,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50365,7 +51120,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50692,7 +51452,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51019,7 +51784,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN82" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51346,7 +52116,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51673,7 +52448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN84" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52000,7 +52780,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52327,7 +53112,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN86" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52654,7 +53444,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52981,7 +53776,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53308,7 +54108,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53635,7 +54440,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN90" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53962,7 +54772,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53970,8 +54785,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
